--- a/results/link-prediction-gcn/Link/5shot/CiteSeer/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/5shot/CiteSeer/GCN_total_results.xlsx
@@ -893,7 +893,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.5022±0.0000</t>
+          <t>0.5000±0.0000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4864±0.0141</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.4956±0.0000</t>
+          <t>0.4897±0.0204</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -923,37 +923,37 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6092±0.0781</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6626±0.0000</t>
+          <t>0.6432±0.0221</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6626±0.0000</t>
+          <t>0.6432±0.0221</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6626±0.0000</t>
+          <t>0.6432±0.0221</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6073±0.0769</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5582±0.0000</t>
+          <t>0.5861±0.0134</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6648±0.0000</t>
+          <t>0.6469±0.0331</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -968,12 +968,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.4901±0.0000</t>
+          <t>0.4747±0.0173</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.4956±0.0000</t>
+          <t>0.5300±0.0436</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -988,37 +988,37 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6267±0.0896</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5436±0.0624</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5436±0.0624</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5436±0.0624</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6256±0.0889</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6725±0.0000</t>
+          <t>0.6982±0.0175</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5531±0.0751</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.4835±0.0000</t>
+          <t>0.4722±0.0166</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.4989±0.0000</t>
+          <t>0.4949±0.0114</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1053,62 +1053,62 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5473±0.0668</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6469±0.0036</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6469±0.0036</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6469±0.0036</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5484±0.0684</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5538±0.0000</t>
+          <t>0.6465±0.0454</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6612±0.0171</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5015±0.0422</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5846±0.0000</t>
+          <t>0.6901±0.0039</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.4901±0.0000</t>
+          <t>0.4799±0.0061</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4747±0.0000</t>
+          <t>0.5165±0.0036</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5022±0.0000</t>
+          <t>0.5000±0.0000</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -1118,42 +1118,42 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.6077±0.0000</t>
+          <t>0.6923±0.0077</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.6505±0.0000</t>
+          <t>0.7319±0.0094</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.6505±0.0000</t>
+          <t>0.7319±0.0094</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.6505±0.0000</t>
+          <t>0.7319±0.0094</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.6055±0.0000</t>
+          <t>0.6952±0.0029</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.6451±0.0000</t>
+          <t>0.6967±0.0080</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.6484±0.0000</t>
+          <t>0.7198±0.0047</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4806±0.0275</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.4758±0.0000</t>
+          <t>0.4971±0.0288</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.4901±0.0000</t>
+          <t>0.4956±0.0071</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1188,17 +1188,17 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5978±0.0000</t>
+          <t>0.6260±0.0171</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5978±0.0000</t>
+          <t>0.6260±0.0171</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5978±0.0000</t>
+          <t>0.6260±0.0171</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6410±0.0172</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4751±0.0180</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.4989±0.0000</t>
+          <t>0.4978±0.0091</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1253,17 +1253,17 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6300±0.0221</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6300±0.0221</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6300±0.0221</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5330±0.0398</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.6337±0.0249</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5044±0.0000</t>
+          <t>0.5022±0.0016</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.4615±0.0000</t>
+          <t>0.4824±0.0247</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.4549±0.0000</t>
+          <t>0.5179±0.0201</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1313,37 +1313,37 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5154±0.0000</t>
+          <t>0.5418±0.0552</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5374±0.0000</t>
+          <t>0.5575±0.0104</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5374±0.0000</t>
+          <t>0.5575±0.0104</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5374±0.0000</t>
+          <t>0.5575±0.0104</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5209±0.0000</t>
+          <t>0.5670±0.0032</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5769±0.0000</t>
+          <t>0.6516±0.0282</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5352±0.0000</t>
+          <t>0.5615±0.0135</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0088±0.0000</t>
+          <t>0.6667±0.0000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,447 +1365,447 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.6385±0.0204</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6285±0.0105</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6582±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6983±0.0237</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.7243±0.0117</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.7243±0.0117</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.7243±0.0117</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.7016±0.0247</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6564±0.0088</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.7262±0.0132</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6186±0.0241</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6437±0.0250</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7422±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7422±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7422±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6378±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7426±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7172±0.0359</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0272</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0272</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6854±0.0272</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7190±0.0371</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7532±0.0075</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.6884±0.0307</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6527±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6477±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6253±0.0265</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6503±0.0110</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6745±0.0111</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.7037±0.0115</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.7037±0.0115</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.7037±0.0115</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0125</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.7301±0.0188</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.7146±0.0143</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.4026±0.2847</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7541±0.0025</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6376±0.0103</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6459±0.0095</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7554±0.0043</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7755±0.0070</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7755±0.0070</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7755±0.0070</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7572±0.0021</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7544±0.0081</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7668±0.0026</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.2021±0.2858</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6353±0.0247</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6361±0.0090</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7367±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6957±0.0092</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6957±0.0092</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6957±0.0092</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6466±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6622±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6944±0.0124</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6305±0.0266</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6562±0.0087</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6891±0.0125</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6891±0.0125</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6891±0.0125</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6772±0.0143</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6927±0.0167</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6891±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6676±0.0007</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6333±0.0325</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6597±0.0072</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6995±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6563±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6329±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6676±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7095±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7220±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7220±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7220±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7093±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7164±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7222±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6356±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6568±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7034±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7034±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7034±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.7301±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6657±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6686±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6202±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.5994±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6736±0.0000</t>
+          <t>0.6860±0.0257</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6922±0.0052</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6922±0.0052</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6832±0.0000</t>
+          <t>0.6922±0.0052</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.6965±0.0018</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6971±0.0000</t>
+          <t>0.7346±0.0114</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6822±0.0000</t>
+          <t>0.6940±0.0065</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4433±0.0000</t>
+          <t>0.6099±0.0203</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.6878±0.0077</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5438±0.0000</t>
+          <t>0.6298±0.0286</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5831±0.0000</t>
+          <t>0.6332±0.0112</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6481±0.0000</t>
+          <t>0.6713±0.0083</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7267±0.0000</t>
+          <t>0.6944±0.0205</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6427±0.0000</t>
+          <t>0.7382±0.0376</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.8026±0.0000</t>
+          <t>0.7716±0.0170</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8026±0.0000</t>
+          <t>0.7716±0.0170</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.8026±0.0000</t>
+          <t>0.7716±0.0170</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6369±0.0000</t>
+          <t>0.7389±0.0351</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6567±0.0000</t>
+          <t>0.6875±0.0118</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7977±0.0000</t>
+          <t>0.7800±0.0038</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5456±0.0000</t>
+          <t>0.5554±0.0501</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7367±0.0204</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.6903±0.0000</t>
+          <t>0.6350±0.0515</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.7062±0.0000</t>
+          <t>0.6962±0.0266</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6434±0.0000</t>
+          <t>0.6509±0.0098</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6067±0.0000</t>
+          <t>0.6516±0.0060</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7312±0.0000</t>
+          <t>0.7949±0.0127</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7597±0.0000</t>
+          <t>0.7893±0.0171</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7597±0.0000</t>
+          <t>0.7893±0.0171</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7597±0.0000</t>
+          <t>0.7893±0.0171</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7491±0.0000</t>
+          <t>0.8095±0.0108</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7733±0.0000</t>
+          <t>0.7938±0.0074</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7844±0.0000</t>
+          <t>0.8024±0.0106</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5402±0.0000</t>
+          <t>0.5326±0.0511</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6392±0.0000</t>
+          <t>0.6524±0.0100</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.5833±0.0000</t>
+          <t>0.6022±0.0152</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5963±0.0000</t>
+          <t>0.6824±0.0038</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6404±0.0000</t>
+          <t>0.6568±0.0088</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6562±0.0000</t>
+          <t>0.6569±0.0074</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.6051±0.0000</t>
+          <t>0.6508±0.0599</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5910±0.0000</t>
+          <t>0.7387±0.0051</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5910±0.0000</t>
+          <t>0.7387±0.0051</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5910±0.0000</t>
+          <t>0.7387±0.0051</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.6172±0.0000</t>
+          <t>0.6584±0.0506</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8345±0.0000</t>
+          <t>0.8372±0.0067</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5779±0.0000</t>
+          <t>0.7370±0.0140</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5653±0.0000</t>
+          <t>0.5766±0.0264</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.7260±0.0000</t>
+          <t>0.8290±0.0034</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.5696±0.0000</t>
+          <t>0.6435±0.0388</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5822±0.0000</t>
+          <t>0.6947±0.0189</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6802±0.0000</t>
+          <t>0.6823±0.0235</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6474±0.0000</t>
+          <t>0.6781±0.0245</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.7193±0.0000</t>
+          <t>0.8282±0.0016</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7522±0.0000</t>
+          <t>0.8341±0.0025</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7522±0.0000</t>
+          <t>0.8341±0.0025</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7522±0.0000</t>
+          <t>0.8341±0.0025</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7376±0.0000</t>
+          <t>0.8247±0.0062</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7692±0.0000</t>
+          <t>0.8347±0.0009</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7483±0.0000</t>
+          <t>0.8261±0.0062</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6082±0.0000</t>
+          <t>0.5455±0.1173</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6345±0.0000</t>
+          <t>0.6487±0.0098</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5812±0.0000</t>
+          <t>0.6219±0.0181</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5837±0.0000</t>
+          <t>0.6814±0.0076</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6420±0.0000</t>
+          <t>0.6543±0.0108</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6465±0.0000</t>
+          <t>0.6558±0.0074</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6388±0.0000</t>
+          <t>0.6572±0.0127</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.7251±0.0037</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.7251±0.0037</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.7251±0.0037</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6393±0.0000</t>
+          <t>0.6605±0.0113</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.4841±0.0000</t>
+          <t>0.6714±0.1312</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7208±0.0160</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.5922±0.0000</t>
+          <t>0.5449±0.0934</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6369±0.0000</t>
+          <t>0.6647±0.0079</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5763±0.0000</t>
+          <t>0.6064±0.0047</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5825±0.0000</t>
+          <t>0.6280±0.0462</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6427±0.0000</t>
+          <t>0.6554±0.0131</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6425±0.0000</t>
+          <t>0.6552±0.0105</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6562±0.0000</t>
+          <t>0.6729±0.0191</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6635±0.0000</t>
+          <t>0.7254±0.0181</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6635±0.0000</t>
+          <t>0.7254±0.0181</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6635±0.0000</t>
+          <t>0.7254±0.0181</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6563±0.0000</t>
+          <t>0.6735±0.0125</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6556±0.0000</t>
+          <t>0.7743±0.0430</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6557±0.0000</t>
+          <t>0.7171±0.0268</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5543±0.0000</t>
+          <t>0.5576±0.0144</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.6959±0.0000</t>
+          <t>0.7359±0.0268</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.5231±0.0000</t>
+          <t>0.6406±0.1089</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.6148±0.0000</t>
+          <t>0.7105±0.0276</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6294±0.0000</t>
+          <t>0.6495±0.0123</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5945±0.0000</t>
+          <t>0.6143±0.0365</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7427±0.0000</t>
+          <t>0.8033±0.0065</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7028±0.0000</t>
+          <t>0.7763±0.0102</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7028±0.0000</t>
+          <t>0.7763±0.0102</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7028±0.0000</t>
+          <t>0.7763±0.0102</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7398±0.0000</t>
+          <t>0.7863±0.0116</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7782±0.0000</t>
+          <t>0.8256±0.0110</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6887±0.0000</t>
+          <t>0.7668±0.0092</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.5131±0.0000</t>
+          <t>0.6706±0.0167</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7148±0.0000</t>
+          <t>0.7301±0.0111</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5624±0.0000</t>
+          <t>0.7022±0.0187</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.7045±0.0066</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6572±0.0000</t>
+          <t>0.6889±0.0206</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7300±0.0000</t>
+          <t>0.7030±0.0144</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6980±0.0000</t>
+          <t>0.7605±0.0187</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.7909±0.0000</t>
+          <t>0.7764±0.0128</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.7909±0.0000</t>
+          <t>0.7764±0.0128</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.7909±0.0000</t>
+          <t>0.7764±0.0128</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6912±0.0000</t>
+          <t>0.7580±0.0176</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7047±0.0000</t>
+          <t>0.7439±0.0136</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7870±0.0000</t>
+          <t>0.7815±0.0091</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6308±0.0000</t>
+          <t>0.6297±0.0405</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7333±0.0000</t>
+          <t>0.7388±0.0123</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.7176±0.0000</t>
+          <t>0.6610±0.0675</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7357±0.0247</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6500±0.0000</t>
+          <t>0.6719±0.0112</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6549±0.0000</t>
+          <t>0.6735±0.0045</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7261±0.0000</t>
+          <t>0.7929±0.0212</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7929±0.0138</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7929±0.0138</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7458±0.0000</t>
+          <t>0.7929±0.0138</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7366±0.0000</t>
+          <t>0.8077±0.0150</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7484±0.0000</t>
+          <t>0.7672±0.0072</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7745±0.0000</t>
+          <t>0.7991±0.0090</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.5934±0.0000</t>
+          <t>0.5989±0.0559</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6513±0.0000</t>
+          <t>0.6781±0.0090</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6724±0.0000</t>
+          <t>0.6937±0.0126</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6815±0.0000</t>
+          <t>0.7323±0.0059</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6482±0.0000</t>
+          <t>0.6747±0.0130</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6651±0.0000</t>
+          <t>0.6769±0.0134</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6515±0.0000</t>
+          <t>0.6834±0.0438</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6430±0.0000</t>
+          <t>0.7511±0.0043</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6430±0.0000</t>
+          <t>0.7511±0.0043</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6430±0.0000</t>
+          <t>0.7511±0.0043</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6572±0.0000</t>
+          <t>0.6903±0.0332</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8477±0.0000</t>
+          <t>0.8430±0.0129</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6421±0.0000</t>
+          <t>0.7425±0.0169</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6185±0.0000</t>
+          <t>0.6492±0.0212</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.8246±0.0031</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6879±0.0432</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5974±0.0000</t>
+          <t>0.7306±0.0412</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6709±0.0000</t>
+          <t>0.7027±0.0088</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6318±0.0000</t>
+          <t>0.7044±0.0217</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6986±0.0000</t>
+          <t>0.8240±0.0042</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.8218±0.0029</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.8218±0.0029</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.8218±0.0029</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7185±0.0000</t>
+          <t>0.8188±0.0012</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.8218±0.0020</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7380±0.0000</t>
+          <t>0.8136±0.0098</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6580±0.0000</t>
+          <t>0.6302±0.0873</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6248±0.0000</t>
+          <t>0.6611±0.0099</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6691±0.0000</t>
+          <t>0.6989±0.0043</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6705±0.0000</t>
+          <t>0.7323±0.0028</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6489±0.0000</t>
+          <t>0.6696±0.0161</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6535±0.0000</t>
+          <t>0.6731±0.0138</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6556±0.0000</t>
+          <t>0.6821±0.0140</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6922±0.0000</t>
+          <t>0.7388±0.0090</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6922±0.0000</t>
+          <t>0.7388±0.0090</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6922±0.0000</t>
+          <t>0.7388±0.0090</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6566±0.0000</t>
+          <t>0.6838±0.0132</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5874±0.0000</t>
+          <t>0.7324±0.0966</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7416±0.0000</t>
+          <t>0.7303±0.0172</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6306±0.0000</t>
+          <t>0.6194±0.0698</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6413±0.0000</t>
+          <t>0.6625±0.0009</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6692±0.0000</t>
+          <t>0.6944±0.0065</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6724±0.0000</t>
+          <t>0.7026±0.0273</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6501±0.0000</t>
+          <t>0.6719±0.0121</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.6497±0.0000</t>
+          <t>0.6726±0.0140</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.6878±0.0181</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.7370±0.0219</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.7370±0.0219</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.7370±0.0219</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6698±0.0000</t>
+          <t>0.6906±0.0175</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7362±0.0000</t>
+          <t>0.8157±0.0362</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6750±0.0000</t>
+          <t>0.7258±0.0305</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6098±0.0000</t>
+          <t>0.6235±0.0163</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.6785±0.0000</t>
+          <t>0.7260±0.0272</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5189±0.0000</t>
+          <t>0.6589±0.1172</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.6242±0.0000</t>
+          <t>0.6986±0.0282</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6444±0.0000</t>
+          <t>0.6671±0.0101</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6212±0.0000</t>
+          <t>0.6328±0.0269</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7265±0.0000</t>
+          <t>0.7860±0.0042</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6527±0.0000</t>
+          <t>0.7355±0.0182</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6527±0.0000</t>
+          <t>0.7355±0.0182</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6527±0.0000</t>
+          <t>0.7355±0.0182</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7189±0.0000</t>
+          <t>0.7673±0.0151</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7610±0.0000</t>
+          <t>0.8053±0.0182</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6350±0.0000</t>
+          <t>0.7185±0.0104</t>
         </is>
       </c>
     </row>
